--- a/data/pupil/3_processed/15_semantic_similarity/mean/sub_1028_cosine_similarity_story_avg.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/mean/sub_1028_cosine_similarity_story_avg.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Dont Look</t>
         </is>
       </c>
@@ -472,6 +477,9 @@
         <v>0.1118070303164332</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.05881439794981619</v>
       </c>
     </row>
